--- a/results/04_final_refined_daily_hydroclimate_data/702/Dry_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Dry_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -413,8 +413,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
+      <c r="D2">
+        <v>22.1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -427,8 +427,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="D3">
+        <v>19.5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -441,8 +441,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
+      <c r="D4">
+        <v>15.8</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>18.9</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -469,8 +469,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>4</v>
+      <c r="D6">
+        <v>18.7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>22.1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -497,8 +497,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>21.3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -511,8 +511,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>4</v>
+      <c r="D9">
+        <v>19.6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>14.5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -539,8 +539,8 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>4</v>
+      <c r="D11">
+        <v>20.7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -819,8 +819,8 @@
       <c r="C31">
         <v>1</v>
       </c>
-      <c r="D31">
-        <v>17.8</v>
+      <c r="D31" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -833,8 +833,8 @@
       <c r="C32">
         <v>2</v>
       </c>
-      <c r="D32">
-        <v>20.3</v>
+      <c r="D32" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -847,8 +847,8 @@
       <c r="C33">
         <v>3</v>
       </c>
-      <c r="D33">
-        <v>18.8</v>
+      <c r="D33" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -861,8 +861,8 @@
       <c r="C34">
         <v>4</v>
       </c>
-      <c r="D34">
-        <v>18.8</v>
+      <c r="D34" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -875,8 +875,8 @@
       <c r="C35">
         <v>5</v>
       </c>
-      <c r="D35">
-        <v>19.8</v>
+      <c r="D35" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -889,8 +889,8 @@
       <c r="C36">
         <v>6</v>
       </c>
-      <c r="D36">
-        <v>18.86</v>
+      <c r="D36" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -903,8 +903,8 @@
       <c r="C37">
         <v>7</v>
       </c>
-      <c r="D37">
-        <v>21.2</v>
+      <c r="D37" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -917,8 +917,8 @@
       <c r="C38">
         <v>8</v>
       </c>
-      <c r="D38">
-        <v>20.8</v>
+      <c r="D38" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -931,8 +931,8 @@
       <c r="C39">
         <v>9</v>
       </c>
-      <c r="D39">
-        <v>20.6</v>
+      <c r="D39" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -945,8 +945,8 @@
       <c r="C40">
         <v>10</v>
       </c>
-      <c r="D40">
-        <v>19.2</v>
+      <c r="D40" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -973,8 +973,8 @@
       <c r="C42">
         <v>12</v>
       </c>
-      <c r="D42" t="s">
-        <v>4</v>
+      <c r="D42">
+        <v>19.4</v>
       </c>
     </row>
     <row r="43" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/702/Dry_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Dry_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Dry_bulb_temp_18h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -693,8 +690,8 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
-        <v>4</v>
+      <c r="D22">
+        <v>21.4</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -707,8 +704,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>4</v>
+      <c r="D23">
+        <v>19.4</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -721,8 +718,8 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
-        <v>4</v>
+      <c r="D24">
+        <v>18.7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -735,8 +732,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
-        <v>4</v>
+      <c r="D25">
+        <v>20.8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -749,8 +746,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
-        <v>4</v>
+      <c r="D26">
+        <v>20.6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -763,8 +760,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>21.7</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -777,8 +774,8 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
-        <v>4</v>
+      <c r="D28">
+        <v>19.7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -791,8 +788,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -805,8 +802,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -819,8 +816,8 @@
       <c r="C31">
         <v>1</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
+      <c r="D31">
+        <v>17.8</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -833,8 +830,8 @@
       <c r="C32">
         <v>2</v>
       </c>
-      <c r="D32" t="s">
-        <v>4</v>
+      <c r="D32">
+        <v>20.3</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -847,8 +844,8 @@
       <c r="C33">
         <v>3</v>
       </c>
-      <c r="D33" t="s">
-        <v>4</v>
+      <c r="D33">
+        <v>18.8</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -861,8 +858,8 @@
       <c r="C34">
         <v>4</v>
       </c>
-      <c r="D34" t="s">
-        <v>4</v>
+      <c r="D34">
+        <v>18.8</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -875,8 +872,8 @@
       <c r="C35">
         <v>5</v>
       </c>
-      <c r="D35" t="s">
-        <v>4</v>
+      <c r="D35">
+        <v>19.8</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -889,8 +886,8 @@
       <c r="C36">
         <v>6</v>
       </c>
-      <c r="D36" t="s">
-        <v>4</v>
+      <c r="D36">
+        <v>18.6</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -903,8 +900,8 @@
       <c r="C37">
         <v>7</v>
       </c>
-      <c r="D37" t="s">
-        <v>4</v>
+      <c r="D37">
+        <v>21.2</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -917,8 +914,8 @@
       <c r="C38">
         <v>8</v>
       </c>
-      <c r="D38" t="s">
-        <v>4</v>
+      <c r="D38">
+        <v>20.8</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -931,8 +928,8 @@
       <c r="C39">
         <v>9</v>
       </c>
-      <c r="D39" t="s">
-        <v>4</v>
+      <c r="D39">
+        <v>20.6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -945,8 +942,8 @@
       <c r="C40">
         <v>10</v>
       </c>
-      <c r="D40" t="s">
-        <v>4</v>
+      <c r="D40">
+        <v>19.2</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -987,8 +984,8 @@
       <c r="C43">
         <v>13</v>
       </c>
-      <c r="D43" t="s">
-        <v>4</v>
+      <c r="D43">
+        <v>19.2</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1001,8 +998,8 @@
       <c r="C44">
         <v>14</v>
       </c>
-      <c r="D44" t="s">
-        <v>4</v>
+      <c r="D44">
+        <v>16.6</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1015,8 +1012,8 @@
       <c r="C45">
         <v>15</v>
       </c>
-      <c r="D45" t="s">
-        <v>4</v>
+      <c r="D45">
+        <v>18.9</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1029,8 +1026,8 @@
       <c r="C46">
         <v>16</v>
       </c>
-      <c r="D46" t="s">
-        <v>4</v>
+      <c r="D46">
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1043,8 +1040,8 @@
       <c r="C47">
         <v>17</v>
       </c>
-      <c r="D47" t="s">
-        <v>4</v>
+      <c r="D47">
+        <v>15.6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1057,8 +1054,8 @@
       <c r="C48">
         <v>18</v>
       </c>
-      <c r="D48" t="s">
-        <v>4</v>
+      <c r="D48">
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1085,8 +1082,8 @@
       <c r="C50">
         <v>20</v>
       </c>
-      <c r="D50" t="s">
-        <v>4</v>
+      <c r="D50">
+        <v>15.8</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1128,7 +1125,7 @@
         <v>23</v>
       </c>
       <c r="D53">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1142,7 +1139,7 @@
         <v>24</v>
       </c>
       <c r="D54">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1169,8 +1166,8 @@
       <c r="C56">
         <v>26</v>
       </c>
-      <c r="D56" t="s">
-        <v>4</v>
+      <c r="D56">
+        <v>21.5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1183,8 +1180,8 @@
       <c r="C57">
         <v>27</v>
       </c>
-      <c r="D57" t="s">
-        <v>4</v>
+      <c r="D57">
+        <v>22.3</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1197,8 +1194,8 @@
       <c r="C58">
         <v>28</v>
       </c>
-      <c r="D58" t="s">
-        <v>4</v>
+      <c r="D58">
+        <v>21.7</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1211,8 +1208,8 @@
       <c r="C59">
         <v>29</v>
       </c>
-      <c r="D59" t="s">
-        <v>4</v>
+      <c r="D59">
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1225,8 +1222,8 @@
       <c r="C60">
         <v>30</v>
       </c>
-      <c r="D60" t="s">
-        <v>4</v>
+      <c r="D60">
+        <v>21.4</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Dry_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Dry_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>Dry_bulb_temp_18h00</t>
+  </si>
+  <si>
+    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -1026,8 +1029,8 @@
       <c r="C46">
         <v>16</v>
       </c>
-      <c r="D46">
-        <v>17</v>
+      <c r="D46" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1040,8 +1043,8 @@
       <c r="C47">
         <v>17</v>
       </c>
-      <c r="D47">
-        <v>15.6</v>
+      <c r="D47" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1054,8 +1057,8 @@
       <c r="C48">
         <v>18</v>
       </c>
-      <c r="D48">
-        <v>19</v>
+      <c r="D48" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1082,8 +1085,8 @@
       <c r="C50">
         <v>20</v>
       </c>
-      <c r="D50">
-        <v>15.8</v>
+      <c r="D50" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/702/Dry_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Dry_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -1071,8 +1071,8 @@
       <c r="C49">
         <v>19</v>
       </c>
-      <c r="D49">
-        <v>17.2</v>
+      <c r="D49" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:4">
